--- a/datasets/commission_formation/data/output/formation_timeline.xlsx
+++ b/datasets/commission_formation/data/output/formation_timeline.xlsx
@@ -747,7 +747,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Last round of Commissioner-designate hearings held, including for Ribera and Fitto (controversial EVPs).</t>
+          <t>Final day of hearings: all six Executive Vice-President-level nominees heard (Fitto, Kallas, Mînzatu, Séjourné, Ribera, Virkkunen).</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -760,7 +760,11 @@
           <t>European Parliament</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241004IPR24465/ep-leaders-adopt-calendar-for-commissioners-designate-hearings</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,17 +774,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Conference of Presidents endorses full College</t>
+          <t>Conference of Presidents concludes hearings process</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EP Conference of Presidents confirms all Commissioners-designate have passed their hearings.</t>
+          <t>EP Conference of Presidents formally declares the hearings process closed and authorises publication of the evaluation letters, following the Conference of Committee Chairs review on 26 November.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -793,7 +797,11 @@
           <t>European Parliament</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.europarl.europa.eu/news/en/press-room/20241127IPR25626/ep-leaders-formally-conclude-the-hearings-process-of-commissioners-designate</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -894,7 +902,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/c29e1593-5a07-4e88-b75e-3f39da3c0e1c_en?filename=COM_2025_45_1_EN.pdf</t>
+          <t>https://eur-lex.europa.eu/legal-content/EN/TXT/?uri=CELEX:52025DC0045</t>
         </is>
       </c>
     </row>
